--- a/Stock_OneClick/history/scan_result_20260530_204551.xlsx
+++ b/Stock_OneClick/history/scan_result_20260530_204551.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q98"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -638,24 +638,6 @@
       <c r="J3" t="n">
         <v>158.41</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-29; 相对D0=-12.72%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -707,24 +689,12 @@
       <c r="J4" s="5" t="n">
         <v>195.88</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-29; 相对D0=-3.46%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -776,24 +746,12 @@
       <c r="J5" s="5" t="n">
         <v>171.66</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-29; 相对D0=2.56%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -845,24 +803,12 @@
       <c r="J6" s="5" t="n">
         <v>52.75</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-29; 相对D0=13.37%</t>
@@ -914,24 +860,6 @@
       <c r="J7" t="n">
         <v>16.6</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-29; 相对D0=2.98%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -983,24 +911,12 @@
       <c r="J8" s="5" t="n">
         <v>191.1</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-29; 相对D0=6.13%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -1052,24 +968,12 @@
       <c r="J9" s="5" t="n">
         <v>48.42</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-29; 相对D0=0.62%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -1121,24 +1025,6 @@
       <c r="J10" t="n">
         <v>133.38</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-29; 相对D0=-5.55%</t>
@@ -1190,24 +1076,6 @@
       <c r="J11" t="n">
         <v>400.6</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-29; 相对D0=2.36%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1259,24 +1127,6 @@
       <c r="J12" t="n">
         <v>968.3200000000001</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-29; 相对D0=-6.78%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1328,24 +1178,12 @@
       <c r="J13" s="5" t="n">
         <v>182.47</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-29; 相对D0=1.73%; 历史重复2次; 重复日期=2026-05-26, 2026-05-28</t>
@@ -1397,24 +1235,12 @@
       <c r="J14" s="5" t="n">
         <v>335.55</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-29; 相对D0=2.89%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -1466,24 +1292,6 @@
       <c r="J15" t="n">
         <v>23.9</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-29; 相对D0=6.18%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1535,24 +1343,6 @@
       <c r="J16" t="n">
         <v>250</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-29; 相对D0=7.76%</t>
@@ -1604,24 +1394,6 @@
       <c r="J17" t="n">
         <v>156.4</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-29; 相对D0=19.85%</t>
@@ -1673,24 +1445,12 @@
       <c r="J18" s="5" t="n">
         <v>258.24</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-29; 相对D0=-1.53%; 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -1742,24 +1502,12 @@
       <c r="J19" s="5" t="n">
         <v>107.61</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-29; 相对D0=25.98%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -1811,24 +1559,12 @@
       <c r="J20" s="5" t="n">
         <v>435.79</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-29; 相对D0=2.30%</t>
@@ -1880,24 +1616,12 @@
       <c r="J21" s="5" t="n">
         <v>13.77</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-29; 相对D0=5.76%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -1949,24 +1673,12 @@
       <c r="J22" s="5" t="n">
         <v>69.56</v>
       </c>
-      <c r="K22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-05-29; 相对D0=-5.31%</t>
@@ -2018,24 +1730,6 @@
       <c r="J23" t="n">
         <v>446.77</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-05-29; 相对D0=5.87%</t>
@@ -2087,24 +1781,6 @@
       <c r="J24" t="n">
         <v>88.91</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-05-29; 相对D0=2.80%</t>
@@ -2156,24 +1832,12 @@
       <c r="J25" s="5" t="n">
         <v>112.7</v>
       </c>
-      <c r="K25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-05-29; 相对D0=4.19%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2225,24 +1889,6 @@
       <c r="J26" t="n">
         <v>109.53</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-05-29; 相对D0=3.44%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2294,24 +1940,6 @@
       <c r="J27" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-05-29; 相对D0=1.12%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -2363,24 +1991,6 @@
       <c r="J28" t="n">
         <v>163.35</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-05-29; 相对D0=3.16%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -2432,24 +2042,12 @@
       <c r="J29" s="5" t="n">
         <v>380.34</v>
       </c>
-      <c r="K29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-05-29; 相对D0=-2.20%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2501,24 +2099,12 @@
       <c r="J30" s="5" t="n">
         <v>632.51</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-05-29; 相对D0=3.29%</t>
@@ -2570,24 +2156,12 @@
       <c r="J31" s="5" t="n">
         <v>66.88</v>
       </c>
-      <c r="K31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-05-29; 相对D0=-2.65%</t>
@@ -2639,24 +2213,6 @@
       <c r="J32" t="n">
         <v>106.39</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-05-29; 相对D0=-0.51%</t>
@@ -2708,24 +2264,12 @@
       <c r="J33" s="5" t="n">
         <v>12.67</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-05-29; 相对D0=3.68%</t>
@@ -2777,24 +2321,6 @@
       <c r="J34" t="n">
         <v>84.23</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-05-29; 相对D0=-0.48%</t>
@@ -2846,24 +2372,12 @@
       <c r="J35" s="5" t="n">
         <v>18.22</v>
       </c>
-      <c r="K35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-05-29; 相对D0=-0.98%</t>
@@ -2915,24 +2429,6 @@
       <c r="J36" t="n">
         <v>315.71</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-05-29; 相对D0=-2.53%</t>
@@ -2984,24 +2480,12 @@
       <c r="J37" s="5" t="n">
         <v>270.64</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-05-29; 相对D0=-0.45%</t>
@@ -3053,24 +2537,6 @@
       <c r="J38" t="n">
         <v>91.5</v>
       </c>
-      <c r="K38" t="n">
-        <v/>
-      </c>
-      <c r="L38" t="n">
-        <v/>
-      </c>
-      <c r="M38" t="n">
-        <v/>
-      </c>
-      <c r="N38" t="n">
-        <v/>
-      </c>
-      <c r="O38" t="n">
-        <v/>
-      </c>
-      <c r="P38" t="n">
-        <v/>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-05-29; 相对D0=0.69%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3122,24 +2588,6 @@
       <c r="J39" t="n">
         <v>35.48</v>
       </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-05-29; 相对D0=-14.20%</t>
@@ -3191,24 +2639,12 @@
       <c r="J40" s="5" t="n">
         <v>124.37</v>
       </c>
-      <c r="K40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-05-29; 相对D0=21.79%</t>
@@ -3260,24 +2696,6 @@
       <c r="J41" t="n">
         <v>225.78</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-05-29; 相对D0=18.23%</t>
@@ -3329,24 +2747,6 @@
       <c r="J42" t="n">
         <v>285</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-05-29; 相对D0=-1.73%</t>
@@ -3398,24 +2798,12 @@
       <c r="J43" s="5" t="n">
         <v>731</v>
       </c>
-      <c r="K43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-05-29; 相对D0=8.94%</t>
@@ -3467,24 +2855,6 @@
       <c r="J44" t="n">
         <v>66.94</v>
       </c>
-      <c r="K44" t="n">
-        <v/>
-      </c>
-      <c r="L44" t="n">
-        <v/>
-      </c>
-      <c r="M44" t="n">
-        <v/>
-      </c>
-      <c r="N44" t="n">
-        <v/>
-      </c>
-      <c r="O44" t="n">
-        <v/>
-      </c>
-      <c r="P44" t="n">
-        <v/>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-05-29; 相对D0=-0.65%</t>
@@ -3536,24 +2906,6 @@
       <c r="J45" t="n">
         <v>1068.04</v>
       </c>
-      <c r="K45" t="n">
-        <v/>
-      </c>
-      <c r="L45" t="n">
-        <v/>
-      </c>
-      <c r="M45" t="n">
-        <v/>
-      </c>
-      <c r="N45" t="n">
-        <v/>
-      </c>
-      <c r="O45" t="n">
-        <v/>
-      </c>
-      <c r="P45" t="n">
-        <v/>
-      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-05-29; 相对D0=-0.13%</t>
@@ -3605,24 +2957,12 @@
       <c r="J46" s="5" t="n">
         <v>137.97</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-05-29; 相对D0=6.38%</t>
@@ -3674,24 +3014,12 @@
       <c r="J47" s="5" t="n">
         <v>101.66</v>
       </c>
-      <c r="K47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-05-29; 相对D0=6.25%</t>
@@ -3743,24 +3071,12 @@
       <c r="J48" s="5" t="n">
         <v>450.24</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-05-29; 相对D0=5.45%</t>
@@ -3812,24 +3128,6 @@
       <c r="J49" t="n">
         <v>231.09</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
-      <c r="L49" t="n">
-        <v/>
-      </c>
-      <c r="M49" t="n">
-        <v/>
-      </c>
-      <c r="N49" t="n">
-        <v/>
-      </c>
-      <c r="O49" t="n">
-        <v/>
-      </c>
-      <c r="P49" t="n">
-        <v/>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-05-29; 相对D0=2.10%</t>
@@ -3881,24 +3179,12 @@
       <c r="J50" s="5" t="n">
         <v>123.27</v>
       </c>
-      <c r="K50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-05-29; 相对D0=30.14%</t>
@@ -3950,24 +3236,12 @@
       <c r="J51" s="5" t="n">
         <v>281.69</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-05-29; 相对D0=9.28%</t>
@@ -4019,24 +3293,12 @@
       <c r="J52" s="5" t="n">
         <v>156.54</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-05-29; 相对D0=9.21%</t>
@@ -4088,24 +3350,12 @@
       <c r="J53" s="5" t="n">
         <v>259.21</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -4157,24 +3407,12 @@
       <c r="J54" s="5" t="n">
         <v>287.75</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -4226,24 +3464,12 @@
       <c r="J55" s="5" t="n">
         <v>211.14</v>
       </c>
-      <c r="K55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P55" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -4480,24 +3706,12 @@
       <c r="J67" s="5" t="n">
         <v>38.85</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-29; 相对D0=-6.32%</t>
@@ -4549,24 +3763,12 @@
       <c r="J68" s="5" t="n">
         <v>91.5</v>
       </c>
-      <c r="K68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-05-29; 相对D0=0.95%</t>
@@ -4618,24 +3820,12 @@
       <c r="J69" s="5" t="n">
         <v>182.46</v>
       </c>
-      <c r="K69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-05-29; 相对D0=-1.22%</t>
@@ -4687,24 +3877,12 @@
       <c r="J70" s="5" t="n">
         <v>133.38</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-05-29; 相对D0=-2.07%</t>
@@ -4756,24 +3934,6 @@
       <c r="J71" t="n">
         <v>35.48</v>
       </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
-      <c r="L71" t="n">
-        <v/>
-      </c>
-      <c r="M71" t="n">
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v/>
-      </c>
-      <c r="O71" t="n">
-        <v/>
-      </c>
-      <c r="P71" t="n">
-        <v/>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-05-29; 相对D0=-5.66%</t>
@@ -4825,24 +3985,6 @@
       <c r="J72" t="n">
         <v>335.55</v>
       </c>
-      <c r="K72" t="n">
-        <v/>
-      </c>
-      <c r="L72" t="n">
-        <v/>
-      </c>
-      <c r="M72" t="n">
-        <v/>
-      </c>
-      <c r="N72" t="n">
-        <v/>
-      </c>
-      <c r="O72" t="n">
-        <v/>
-      </c>
-      <c r="P72" t="n">
-        <v/>
-      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-05-29; 相对D0=9.18%</t>
@@ -4894,24 +4036,12 @@
       <c r="J73" s="5" t="n">
         <v>56.63</v>
       </c>
-      <c r="K73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P73" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
+      <c r="N73" s="5" t="n"/>
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="5" t="n"/>
       <c r="Q73" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-05-29; 相对D0=-1.44%</t>
@@ -4963,24 +4093,12 @@
       <c r="J74" s="5" t="n">
         <v>12.29</v>
       </c>
-      <c r="K74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
       <c r="Q74" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-05-29; 相对D0=-7.94%</t>
@@ -5032,24 +4150,12 @@
       <c r="J75" s="5" t="n">
         <v>54.55</v>
       </c>
-      <c r="K75" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M75" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N75" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O75" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P75" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K75" s="5" t="n"/>
+      <c r="L75" s="5" t="n"/>
+      <c r="M75" s="5" t="n"/>
+      <c r="N75" s="5" t="n"/>
+      <c r="O75" s="5" t="n"/>
+      <c r="P75" s="5" t="n"/>
       <c r="Q75" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-05-29; 相对D0=-3.45%</t>
@@ -5101,24 +4207,6 @@
       <c r="J76" t="n">
         <v>139.73</v>
       </c>
-      <c r="K76" t="n">
-        <v/>
-      </c>
-      <c r="L76" t="n">
-        <v/>
-      </c>
-      <c r="M76" t="n">
-        <v/>
-      </c>
-      <c r="N76" t="n">
-        <v/>
-      </c>
-      <c r="O76" t="n">
-        <v/>
-      </c>
-      <c r="P76" t="n">
-        <v/>
-      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-05-29; 相对D0=10.54%</t>
@@ -5170,24 +4258,12 @@
       <c r="J77" s="5" t="n">
         <v>103.16</v>
       </c>
-      <c r="K77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P77" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
       <c r="Q77" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-05-29; 相对D0=-10.84%</t>
@@ -5239,24 +4315,6 @@
       <c r="J78" t="n">
         <v>287.75</v>
       </c>
-      <c r="K78" t="n">
-        <v/>
-      </c>
-      <c r="L78" t="n">
-        <v/>
-      </c>
-      <c r="M78" t="n">
-        <v/>
-      </c>
-      <c r="N78" t="n">
-        <v/>
-      </c>
-      <c r="O78" t="n">
-        <v/>
-      </c>
-      <c r="P78" t="n">
-        <v/>
-      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-05-29; 相对D0=0.50%</t>
@@ -5308,24 +4366,12 @@
       <c r="J79" s="5" t="n">
         <v>181.16</v>
       </c>
-      <c r="K79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-05-29; 相对D0=-0.99%</t>
@@ -5377,24 +4423,6 @@
       <c r="J80" t="n">
         <v>475.62</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-05-29; 相对D0=-1.04%</t>
@@ -5446,24 +4474,6 @@
       <c r="J81" t="n">
         <v>92.33</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -5515,24 +4525,12 @@
       <c r="J82" s="5" t="n">
         <v>69.56</v>
       </c>
-      <c r="K82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P82" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="n"/>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
       <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -5584,24 +4582,12 @@
       <c r="J83" s="5" t="n">
         <v>285</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -5653,24 +4639,12 @@
       <c r="J84" s="5" t="n">
         <v>171.66</v>
       </c>
-      <c r="K84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P84" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="5" t="n"/>
       <c r="Q84" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -5722,24 +4696,12 @@
       <c r="J85" s="5" t="n">
         <v>361.47</v>
       </c>
-      <c r="K85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P85" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="5" t="n"/>
+      <c r="M85" s="5" t="n"/>
+      <c r="N85" s="5" t="n"/>
+      <c r="O85" s="5" t="n"/>
+      <c r="P85" s="5" t="n"/>
       <c r="Q85" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -5791,24 +4753,12 @@
       <c r="J86" s="5" t="n">
         <v>18.88</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -5860,24 +4810,6 @@
       <c r="J87" t="n">
         <v>114.68</v>
       </c>
-      <c r="K87" t="n">
-        <v/>
-      </c>
-      <c r="L87" t="n">
-        <v/>
-      </c>
-      <c r="M87" t="n">
-        <v/>
-      </c>
-      <c r="N87" t="n">
-        <v/>
-      </c>
-      <c r="O87" t="n">
-        <v/>
-      </c>
-      <c r="P87" t="n">
-        <v/>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -5929,24 +4861,6 @@
       <c r="J88" t="n">
         <v>134.08</v>
       </c>
-      <c r="K88" t="n">
-        <v/>
-      </c>
-      <c r="L88" t="n">
-        <v/>
-      </c>
-      <c r="M88" t="n">
-        <v/>
-      </c>
-      <c r="N88" t="n">
-        <v/>
-      </c>
-      <c r="O88" t="n">
-        <v/>
-      </c>
-      <c r="P88" t="n">
-        <v/>
-      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -5998,24 +4912,12 @@
       <c r="J89" s="5" t="n">
         <v>255.23</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-05-29; 相对D0=0.00%</t>
@@ -6112,7 +5014,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6124,7 +5025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -6669,10 +5570,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6684,7 +5581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -6968,7 +5865,6 @@
       <c r="G9" s="13" t="n">
         <v>0.054451</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7000,7 +5896,6 @@
       <c r="G10" s="13" t="n">
         <v>0.020986</v>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -7430,9 +6325,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7444,7 +6336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7512,7 +6404,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -7882,7 +6774,6 @@
       <c r="E22" t="n">
         <v>134.08</v>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -8000,7 +6891,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8574,7 +7464,6 @@
       <c r="D3" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46170</v>
       </c>
@@ -8680,7 +7569,6 @@
       <c r="D5" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="8" t="n">
         <v>46164</v>
       </c>
@@ -8886,7 +7774,6 @@
       <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" s="8" t="n">
         <v>46171</v>
       </c>
@@ -8998,7 +7885,6 @@
       <c r="I4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" s="8" t="n">
         <v>46169</v>
       </c>
@@ -9087,7 +7973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9607,7 +8493,6 @@
       <c r="M10" s="12" t="n">
         <v>-0.055516</v>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -9927,7 +8812,6 @@
       <c r="M16" s="13" t="n">
         <v>0.077586</v>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9977,7 +8861,6 @@
       <c r="M17" s="13" t="n">
         <v>0.198467</v>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -10135,7 +9018,6 @@
       <c r="M20" s="13" t="n">
         <v>0.022957</v>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -10449,11 +9331,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10465,7 +9342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -10626,24 +9503,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10695,24 +9560,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10764,24 +9617,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10833,24 +9674,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10902,24 +9731,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10971,24 +9782,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11040,24 +9839,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11109,24 +9896,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11178,24 +9947,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11247,24 +10004,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11316,24 +10061,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11385,24 +10118,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11454,24 +10175,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11523,24 +10226,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11592,24 +10277,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11661,24 +10328,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11730,24 +10385,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11799,24 +10442,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11868,24 +10493,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -12122,24 +10735,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -12184,11 +10785,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12200,7 +10796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -12372,7 +10968,6 @@
       <c r="K4" s="13" t="n">
         <v>0.058672</v>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -12720,7 +11315,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -12808,7 +11403,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -12876,7 +11471,6 @@
       <c r="K15" s="12" t="n">
         <v>-0.004844</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -12964,7 +11558,6 @@
       <c r="K17" s="12" t="n">
         <v>-0.025316</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18"/>
     <row r="19">
@@ -13524,7 +12117,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
